--- a/data/trans_camb/P34A_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P34A_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,1; -4,96</t>
+          <t>-15,0; -4,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,05; -1,3</t>
+          <t>-12,29; -0,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,71; -3,39</t>
+          <t>-17,64; -2,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,38; -6,79</t>
+          <t>-19,82; -6,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 2,87</t>
+          <t>-11,53; 2,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 3,48</t>
+          <t>-14,08; 3,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-15,42; -7,06</t>
+          <t>-15,51; -7,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,32; -0,56</t>
+          <t>-9,88; -1,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,11; -3,2</t>
+          <t>-14,68; -3,36</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-52,86; -21,1</t>
+          <t>-53,73; -20,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-43,24; -4,96</t>
+          <t>-43,29; -2,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-68,46; -13,08</t>
+          <t>-64,95; -10,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-43,27; -17,48</t>
+          <t>-42,94; -17,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,57; 7,46</t>
+          <t>-24,98; 5,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,39; 9,48</t>
+          <t>-31,4; 9,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-43,53; -22,98</t>
+          <t>-43,61; -22,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,45; -1,71</t>
+          <t>-27,47; -3,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-42,95; -9,88</t>
+          <t>-42,99; -10,33</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,18; -12,43</t>
+          <t>-21,49; -12,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,85; -4,94</t>
+          <t>-14,79; -4,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 5,96</t>
+          <t>-7,71; 6,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-22,5; -11,25</t>
+          <t>-22,61; -11,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,52; -1,99</t>
+          <t>-13,43; -2,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-25,76; -4,67</t>
+          <t>-26,18; -5,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-20,32; -13,18</t>
+          <t>-20,45; -13,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,38; -4,92</t>
+          <t>-12,24; -4,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-14,6; -1,23</t>
+          <t>-14,36; -1,12</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-55,29; -36,51</t>
+          <t>-55,46; -35,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,1; -14,28</t>
+          <t>-38,37; -13,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,82; 17,42</t>
+          <t>-19,99; 19,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-47,65; -26,84</t>
+          <t>-47,99; -27,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,65; -4,77</t>
+          <t>-28,32; -5,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,22; -10,85</t>
+          <t>-57,53; -12,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,19; -34,78</t>
+          <t>-48,51; -34,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,49; -12,65</t>
+          <t>-28,96; -11,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-35,88; -3,28</t>
+          <t>-35,23; -3,17</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-24,31; -13,81</t>
+          <t>-24,59; -13,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,19; -3,45</t>
+          <t>-15,04; -4,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,59; -4,42</t>
+          <t>-15,92; -4,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,6; -11,17</t>
+          <t>-21,64; -10,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,0; -4,53</t>
+          <t>-15,14; -4,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,92; -0,68</t>
+          <t>-11,06; -0,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-21,38; -14,09</t>
+          <t>-21,57; -13,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-13,29; -5,69</t>
+          <t>-13,07; -5,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,22; -4,11</t>
+          <t>-11,87; -4,05</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-52,13; -33,79</t>
+          <t>-52,19; -33,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-30,39; -8,84</t>
+          <t>-31,97; -10,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-33,86; -10,71</t>
+          <t>-33,7; -9,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-45,51; -26,31</t>
+          <t>-45,37; -25,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-31,79; -10,66</t>
+          <t>-32,56; -10,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,01; -1,79</t>
+          <t>-23,19; -1,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-46,1; -33,19</t>
+          <t>-46,69; -32,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,39; -13,34</t>
+          <t>-28,38; -14,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-25,96; -9,57</t>
+          <t>-25,75; -9,52</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-30,39; -18,87</t>
+          <t>-30,14; -18,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,98; -4,98</t>
+          <t>-17,56; -4,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-39,9; -12,21</t>
+          <t>-41,25; -12,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-21,67; -10,32</t>
+          <t>-21,41; -10,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,02; -0,54</t>
+          <t>-11,97; -0,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 4,2</t>
+          <t>-11,58; 4,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-24,15; -16,12</t>
+          <t>-24,52; -16,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,72; -3,77</t>
+          <t>-12,94; -4,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-29,06; -8,32</t>
+          <t>-28,09; -7,9</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-57,85; -40,46</t>
+          <t>-57,71; -39,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-32,41; -10,38</t>
+          <t>-32,94; -10,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-78,52; -25,27</t>
+          <t>-76,99; -25,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-46,27; -25,0</t>
+          <t>-45,87; -24,72</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,46; -1,37</t>
+          <t>-25,23; -1,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-24,05; 10,47</t>
+          <t>-24,6; 10,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-49,39; -35,59</t>
+          <t>-50,66; -35,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-25,63; -8,43</t>
+          <t>-26,39; -10,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-60,6; -18,38</t>
+          <t>-58,2; -17,03</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-31,91; -19,01</t>
+          <t>-32,28; -18,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-21,35; -7,95</t>
+          <t>-21,52; -7,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,78; -5,32</t>
+          <t>-17,14; -4,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-24,49; -11,51</t>
+          <t>-24,24; -11,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 9,38</t>
+          <t>-5,22; 8,98</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,9; -0,6</t>
+          <t>-11,77; 0,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-26,51; -17,43</t>
+          <t>-26,76; -17,06</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-10,77; -1,38</t>
+          <t>-10,86; -1,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-13,05; -4,11</t>
+          <t>-12,76; -4,28</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-59,99; -40,31</t>
+          <t>-60,13; -39,93</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,43; -16,82</t>
+          <t>-39,8; -16,19</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-32,47; -11,15</t>
+          <t>-32,18; -9,67</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-52,44; -28,3</t>
+          <t>-51,69; -28,67</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 23,48</t>
+          <t>-11,04; 22,45</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-25,32; -1,5</t>
+          <t>-24,88; 1,22</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-53,7; -38,73</t>
+          <t>-54,19; -38,55</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-21,74; -3,04</t>
+          <t>-21,72; -1,94</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-25,83; -9,17</t>
+          <t>-25,53; -9,72</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-25,15; -10,28</t>
+          <t>-24,95; -9,53</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 7,28</t>
+          <t>-8,17; 7,17</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-14,25; -1,24</t>
+          <t>-14,88; -1,12</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-21,99; -7,82</t>
+          <t>-21,55; -7,11</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 5,16</t>
+          <t>-8,96; 6,01</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-39,12; -8,7</t>
+          <t>-39,66; -8,67</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-22,06; -10,91</t>
+          <t>-21,86; -10,95</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 3,84</t>
+          <t>-7,09; 3,42</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-31,14; -8,11</t>
+          <t>-30,52; -7,94</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-58,22; -28,45</t>
+          <t>-58,59; -27,85</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-19,76; 20,39</t>
+          <t>-19,08; 20,5</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-33,17; -3,07</t>
+          <t>-33,73; -2,84</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-42,82; -17,36</t>
+          <t>-42,63; -16,59</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-18,64; 11,76</t>
+          <t>-17,61; 13,65</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-78,69; -19,06</t>
+          <t>-78,76; -18,86</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-47,53; -26,37</t>
+          <t>-46,71; -26,6</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 9,42</t>
+          <t>-14,78; 8,25</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-70,59; -19,03</t>
+          <t>-65,83; -18,58</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-31,04; -12,56</t>
+          <t>-30,82; -12,88</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 10,64</t>
+          <t>-6,93; 9,71</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-15,57; 0,64</t>
+          <t>-17,04; -0,72</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-18,0; -1,8</t>
+          <t>-17,28; -1,38</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,55; 16,45</t>
+          <t>-0,2; 15,18</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 8,99</t>
+          <t>-4,5; 8,62</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-20,96; -9,19</t>
+          <t>-20,75; -9,05</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 11,0</t>
+          <t>-0,48; 11,16</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 3,8</t>
+          <t>-6,9; 3,45</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-57,12; -27,54</t>
+          <t>-57,14; -28,73</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 25,16</t>
+          <t>-12,64; 21,65</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-28,68; 1,6</t>
+          <t>-30,56; -1,39</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-27,4; -2,83</t>
+          <t>-26,91; -2,43</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,86; 29,43</t>
+          <t>-0,51; 27,11</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 16,14</t>
+          <t>-6,95; 15,3</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-34,77; -16,91</t>
+          <t>-35,21; -16,9</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 20,41</t>
+          <t>-0,83; 21,35</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 7,27</t>
+          <t>-11,46; 6,65</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-20,97; -16,22</t>
+          <t>-20,83; -16,49</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,66; -4,69</t>
+          <t>-9,75; -4,63</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-17,78; -6,9</t>
+          <t>-16,72; -6,86</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-17,36; -12,67</t>
+          <t>-17,48; -12,8</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-5,96; -1,31</t>
+          <t>-5,77; -0,92</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-15,27; -4,63</t>
+          <t>-16,25; -4,61</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-18,5; -15,23</t>
+          <t>-18,44; -15,26</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-7,09; -3,61</t>
+          <t>-6,95; -3,56</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-13,63; -6,28</t>
+          <t>-13,38; -6,49</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-49,51; -40,56</t>
+          <t>-49,52; -41,25</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-22,79; -11,68</t>
+          <t>-22,99; -11,44</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-42,37; -16,96</t>
+          <t>-40,87; -17,1</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-36,76; -28,18</t>
+          <t>-36,99; -28,46</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-12,5; -2,98</t>
+          <t>-12,33; -2,07</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-32,97; -10,28</t>
+          <t>-34,22; -10,1</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-41,64; -35,53</t>
+          <t>-41,52; -35,45</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-16,06; -8,55</t>
+          <t>-15,55; -8,29</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-31,22; -14,41</t>
+          <t>-30,65; -14,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P34A_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P34A_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-10,97</t>
+          <t>-11,53</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-5,82</t>
+          <t>-6,04</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-9,48</t>
+          <t>-9,18</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,0; -4,52</t>
+          <t>-14,92; -4,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,29; -0,67</t>
+          <t>-12,13; -0,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,64; -2,82</t>
+          <t>-17,73; -3,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,82; -6,94</t>
+          <t>-19,35; -6,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 2,29</t>
+          <t>-10,81; 2,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 3,78</t>
+          <t>-14,74; 2,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-15,51; -7,03</t>
+          <t>-15,67; -7,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,88; -1,12</t>
+          <t>-9,9; -0,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,68; -3,36</t>
+          <t>-14,86; -3,32</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-43,16%</t>
+          <t>-45,37%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-13,67%</t>
+          <t>-14,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-28,12%</t>
+          <t>-27,23%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-53,73; -20,61</t>
+          <t>-52,62; -18,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-43,29; -2,93</t>
+          <t>-42,95; -4,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-64,95; -10,32</t>
+          <t>-63,98; -16,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-42,94; -17,81</t>
+          <t>-42,84; -17,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,98; 5,51</t>
+          <t>-23,68; 5,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,4; 9,57</t>
+          <t>-32,2; 5,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-43,61; -22,27</t>
+          <t>-43,62; -23,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,47; -3,51</t>
+          <t>-28,1; -3,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-42,99; -10,33</t>
+          <t>-42,39; -10,28</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,92</t>
+          <t>-2,94</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-12,4</t>
+          <t>-6,77</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-6,47</t>
+          <t>-4,46</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,49; -12,03</t>
+          <t>-21,08; -11,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,79; -4,36</t>
+          <t>-14,23; -3,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 6,46</t>
+          <t>-9,53; 3,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-22,61; -11,36</t>
+          <t>-22,28; -11,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,43; -2,18</t>
+          <t>-13,21; -2,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,18; -5,33</t>
+          <t>-12,56; -0,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-20,45; -13,3</t>
+          <t>-20,66; -12,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,24; -4,48</t>
+          <t>-12,62; -4,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-14,36; -1,12</t>
+          <t>-9,12; -0,21</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-2,53%</t>
+          <t>-8,08%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-27,67%</t>
+          <t>-15,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-16,08%</t>
+          <t>-11,08%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-55,46; -35,22</t>
+          <t>-55,33; -35,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,37; -13,08</t>
+          <t>-36,94; -11,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-19,99; 19,19</t>
+          <t>-24,1; 11,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-47,99; -27,32</t>
+          <t>-47,16; -26,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,32; -5,09</t>
+          <t>-27,7; -4,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,53; -12,53</t>
+          <t>-26,71; -1,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,51; -34,34</t>
+          <t>-48,75; -34,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,96; -11,82</t>
+          <t>-29,62; -12,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-35,23; -3,17</t>
+          <t>-21,31; -0,46</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-9,97</t>
+          <t>-8,88</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,71</t>
+          <t>-4,98</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-7,83</t>
+          <t>-6,93</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-24,59; -13,87</t>
+          <t>-24,48; -13,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,04; -4,23</t>
+          <t>-14,56; -3,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,92; -4,06</t>
+          <t>-13,85; -2,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,64; -10,95</t>
+          <t>-21,46; -11,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,14; -4,36</t>
+          <t>-15,36; -4,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,06; -0,71</t>
+          <t>-10,05; 0,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-21,57; -13,88</t>
+          <t>-21,45; -14,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-13,07; -5,99</t>
+          <t>-13,36; -5,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,87; -4,05</t>
+          <t>-10,66; -3,22</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-22,49%</t>
+          <t>-20,03%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-12,79%</t>
+          <t>-11,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-17,6%</t>
+          <t>-15,58%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-52,19; -33,38</t>
+          <t>-52,05; -32,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,97; -10,17</t>
+          <t>-30,82; -8,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-33,7; -9,68</t>
+          <t>-30,03; -6,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-45,37; -25,8</t>
+          <t>-44,85; -26,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,56; -10,48</t>
+          <t>-32,34; -10,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,19; -1,67</t>
+          <t>-20,76; 0,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-46,69; -32,63</t>
+          <t>-46,27; -33,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,38; -14,1</t>
+          <t>-28,85; -13,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-25,75; -9,52</t>
+          <t>-22,83; -7,6</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-24,09</t>
+          <t>-13,8</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-5,51</t>
+          <t>-8,96</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-15,55</t>
+          <t>-11,42</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-30,14; -18,25</t>
+          <t>-29,7; -17,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-17,56; -4,97</t>
+          <t>-16,86; -4,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-41,25; -12,26</t>
+          <t>-19,47; -7,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-21,41; -10,12</t>
+          <t>-21,8; -9,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,97; -0,28</t>
+          <t>-11,64; 0,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 4,15</t>
+          <t>-14,17; -3,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-24,52; -16,1</t>
+          <t>-24,38; -16,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,94; -4,48</t>
+          <t>-12,68; -4,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-28,09; -7,9</t>
+          <t>-15,57; -7,59</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-48,77%</t>
+          <t>-27,95%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-12,5%</t>
+          <t>-20,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-33,26%</t>
+          <t>-24,42%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-57,71; -39,58</t>
+          <t>-57,08; -37,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-32,94; -10,76</t>
+          <t>-32,01; -9,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-76,99; -25,13</t>
+          <t>-37,13; -17,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-45,87; -24,72</t>
+          <t>-45,85; -23,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,23; -1,0</t>
+          <t>-25,22; 0,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-24,6; 10,33</t>
+          <t>-29,83; -8,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-50,66; -35,79</t>
+          <t>-49,96; -36,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-26,39; -10,02</t>
+          <t>-25,93; -9,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-58,2; -17,03</t>
+          <t>-31,51; -16,94</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-11,22</t>
+          <t>-11,01</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-6,2</t>
+          <t>-6,41</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-8,6</t>
+          <t>-8,62</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-32,28; -18,85</t>
+          <t>-32,12; -18,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-21,52; -7,4</t>
+          <t>-21,5; -7,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,14; -4,35</t>
+          <t>-17,79; -4,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-24,24; -11,45</t>
+          <t>-24,96; -11,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 8,98</t>
+          <t>-4,51; 9,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 0,49</t>
+          <t>-11,81; -0,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-26,76; -17,06</t>
+          <t>-26,74; -17,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-10,86; -1,06</t>
+          <t>-10,63; -1,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-12,76; -4,28</t>
+          <t>-12,47; -3,97</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-22,21%</t>
+          <t>-21,79%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-14,13%</t>
+          <t>-14,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-18,27%</t>
+          <t>-18,3%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-60,13; -39,93</t>
+          <t>-60,17; -40,74</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,8; -16,19</t>
+          <t>-40,26; -16,05</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-32,18; -9,67</t>
+          <t>-32,64; -9,15</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-51,69; -28,67</t>
+          <t>-52,98; -29,42</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 22,45</t>
+          <t>-9,81; 24,04</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-24,88; 1,22</t>
+          <t>-24,82; -1,34</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-54,19; -38,55</t>
+          <t>-54,22; -38,47</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-21,72; -1,94</t>
+          <t>-21,74; -2,37</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-25,53; -9,72</t>
+          <t>-25,4; -9,34</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-7,66</t>
+          <t>-7,46</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-23,44</t>
+          <t>-10,66</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-16,73</t>
+          <t>-9,31</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-24,95; -9,53</t>
+          <t>-25,16; -9,76</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 7,17</t>
+          <t>-9,06; 6,43</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-14,88; -1,12</t>
+          <t>-14,03; -0,25</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-21,55; -7,11</t>
+          <t>-22,65; -7,82</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 6,01</t>
+          <t>-9,43; 4,92</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-39,66; -8,67</t>
+          <t>-16,64; -4,67</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-21,86; -10,95</t>
+          <t>-21,59; -10,8</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 3,42</t>
+          <t>-6,72; 3,73</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-30,52; -7,94</t>
+          <t>-14,32; -5,0</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-19,72%</t>
+          <t>-19,2%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-48,9%</t>
+          <t>-22,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-38,25%</t>
+          <t>-21,27%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-58,59; -27,85</t>
+          <t>-58,99; -27,53</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 20,5</t>
+          <t>-20,92; 18,92</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-33,73; -2,84</t>
+          <t>-32,82; -0,73</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-42,63; -16,59</t>
+          <t>-44,63; -17,41</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-17,61; 13,65</t>
+          <t>-18,13; 11,26</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-78,76; -18,86</t>
+          <t>-32,16; -10,63</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-46,71; -26,6</t>
+          <t>-46,76; -26,55</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-14,78; 8,25</t>
+          <t>-14,22; 9,01</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-65,83; -18,58</t>
+          <t>-31,02; -12,43</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-7,99</t>
+          <t>-8,18</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,25</t>
+          <t>2,23</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-1,94</t>
+          <t>-2,05</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-30,82; -12,88</t>
+          <t>-31,7; -13,1</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 9,71</t>
+          <t>-6,88; 9,96</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-17,04; -0,72</t>
+          <t>-16,15; -0,02</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-17,28; -1,38</t>
+          <t>-17,3; -1,5</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 15,18</t>
+          <t>0,17; 15,6</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 8,62</t>
+          <t>-4,78; 9,2</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-20,75; -9,05</t>
+          <t>-20,72; -8,18</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 11,16</t>
+          <t>-0,61; 11,2</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 3,45</t>
+          <t>-7,41; 2,81</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-16,15%</t>
+          <t>-16,53%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-3,43%</t>
+          <t>-3,64%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-57,14; -28,73</t>
+          <t>-57,69; -29,25</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 21,65</t>
+          <t>-12,44; 22,26</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-30,56; -1,39</t>
+          <t>-29,1; 0,44</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-26,91; -2,43</t>
+          <t>-27,18; -2,89</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 27,11</t>
+          <t>0,27; 28,21</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 15,3</t>
+          <t>-7,43; 16,51</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-35,21; -16,9</t>
+          <t>-35,23; -15,66</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 21,35</t>
+          <t>-1,0; 21,03</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 6,65</t>
+          <t>-12,22; 5,42</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-10,17</t>
+          <t>-7,62</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-8,17</t>
+          <t>-5,64</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-9,1</t>
+          <t>-6,56</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-20,83; -16,49</t>
+          <t>-20,84; -16,34</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,75; -4,63</t>
+          <t>-9,63; -4,87</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-16,72; -6,86</t>
+          <t>-10,28; -5,18</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-17,48; -12,8</t>
+          <t>-17,47; -12,86</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-5,77; -0,92</t>
+          <t>-5,72; -0,72</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-16,25; -4,61</t>
+          <t>-7,93; -3,44</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-18,44; -15,26</t>
+          <t>-18,42; -15,26</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-6,95; -3,56</t>
+          <t>-7,07; -3,6</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-13,38; -6,49</t>
+          <t>-8,16; -4,88</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-24,77%</t>
+          <t>-18,55%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-17,7%</t>
+          <t>-12,22%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-20,86%</t>
+          <t>-15,04%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-49,52; -41,25</t>
+          <t>-49,31; -40,96</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-22,99; -11,44</t>
+          <t>-22,76; -12,18</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-40,87; -17,1</t>
+          <t>-24,19; -12,97</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-36,99; -28,46</t>
+          <t>-37,11; -28,88</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-12,33; -2,07</t>
+          <t>-12,07; -1,64</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-34,22; -10,1</t>
+          <t>-16,65; -7,64</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-41,52; -35,45</t>
+          <t>-41,4; -35,65</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-15,55; -8,29</t>
+          <t>-15,82; -8,36</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-30,65; -14,9</t>
+          <t>-18,36; -11,49</t>
         </is>
       </c>
     </row>
